--- a/stock_list.xlsx
+++ b/stock_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tacon\tacona1016\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tacon\tacona1016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3931E31A-BC65-4592-B41A-62A0573BF4BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3592A1-7FEE-4F9E-A1E1-65E79A001399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{2576DCEE-6997-41AE-B7C3-97677DC4C085}"/>
   </bookViews>
@@ -36,28 +36,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>ticker</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>KRW=X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>parameter</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>JPYKRW=X</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -86,10 +74,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>composite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>S&amp;P500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -114,10 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>material</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>VIX</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,86 +114,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>US dollar index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DX-Y.NYB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>company</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Apple</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AAPL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NVIDIA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NVDA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microsoft</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MSFT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GOOG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Amazon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMZN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Alphabet1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSMC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Broadcom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AVGO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tesla</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TSLA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>GC=F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -222,7 +122,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Silver</t>
+    <t>TLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>^TNX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>^TYX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국장기채ETF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국채10년물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국채30년물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>은</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alias</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -628,243 +560,131 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5355772-15DF-4893-A932-90B1F9D5F736}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
